--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="436">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -995,6 +995,12 @@
   </si>
   <si>
     <t>2.1.0</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>1.9.0</t>
   </si>
   <si>
     <t>1.6.1</t>
@@ -1159,6 +1165,21 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
+    <t>* Implement architecture changes in time boxed iterations rather than big migrations
+* Track actual cost outcomes vs estimated savings documented in prior trade off analysis
+* Define and monitor success metrics (cost delta, performance, reliability) for each iteration
+* Hold structured retrospectives after each iteration to capture lessons learned
+* Feed iteration outcomes back into the modernization backlog to reprioritize remaining work
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Document and publish cost savings and performance outcomes achieved through architecture changes
+* Update internal architecture reference guides and design patterns with validated approaches
+* Share case studies and reusable blueprints with engineering teams to accelerate adoption
+* Establish a regular cadence to refresh published benefits data and retire outdated references
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>* Process defined for new accounts and resources deployed
 * Train teams on process
 * Automate process
@@ -1173,10 +1194,10 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
-    <t>* Data based on existing patterns
-* Proactive investigations and interviews with teams
-* Proactive self reporting by the business and/or teams
-* 100% catch rate of spikes before they happen
+    <t>* Collect data based on existing patterns observed in spend
+* Conduct proactive investigations and interviews with teams
+* Gather existing self reporting by the business and/or teams
+* Factor in expected increases to the forecast model
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1320,6 +1341,32 @@
 * RCA completed after alerts
 10*Ceil(x/6)
 </t>
+  </si>
+  <si>
+    <t>Denominator: all anomalies detected during the review period. A field item is met when the field is
+populated on 90% or more of those records.
+* Single system of record
+* Scope fields populated (billing account, service, region, and a named accountable owner)
+* Impact fields populated (variance amount in the reporting currency, and the start and end of the
+  period the variance covers)
+* Timeline fields populated (first occurrence, detection, notification, and resolution timestamps)
+* Disposition field populated (true, expected change, or false)
+* Retention and queryability (records retained for at least 13 months and queryable by scope,
+  disposition, and root cause)
+10*Ceil(x/6)</t>
+  </si>
+  <si>
+    <t>Denominator: anomalies recorded with a true positive disposition during the review period. Items 1
+through 4 are met when the stated field is populated on 90% or more of those records.
+1. Owner and due date (each record carries a named accountable owner and an analysis due date)
+2. Root cause recorded (each record carries a root cause entry naming the change that triggered it)
+3. Cause classified (each root cause assigned exactly one category from a published, fixed
+   category list)
+4. Remediation recorded (each record carries a remediation action, its completion date, and the
+   measured spend delta over the period following the fix)
+5. Preventive control registered (every cause category observed 3 or more times in the trailing
+   12 months has a linked policy, guardrail, budget, or detection rule)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Number of detections per time period
@@ -1333,6 +1380,25 @@
 10*Ceil(x/8)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Alert precision (score x4),
+  Missed anomalies (score x3),
+  Tuning cadence (score x2),
+  Tuning governance (score x1).
+  Max raw (50)
+* Alert_Precision: Alerts confirmed as true positives divided by all alerts raised in the review period
+  (0=Not measured, 1&lt;50%, 2=50-69%, 3=70-84%, 4=85-94%, 5=95%+)
+* Missed_Anomalies: Share of anomalies first found by invoice review, budget variance, or an owner
+  (0=Not measured, 1&gt;25%, 2=10-25%, 3=5-9%, 4=1-4%, 5&lt;1%)
+* Tuning_Cadence: How often thresholds are reviewed and adjusted against observed outcomes
+  (0=Never, 1=Ad-hoc, 2=Annual, 3=Quarterly, 4=Monthly, 5=Continuous or automated)
+* Tuning_Governance: How a threshold change is decided and recorded
+  (0=Undocumented, 1=Changed by one person, 2=Documented with rationale,
+  3=Reviewed with the alert recipients, 4=Version controlled and auditable,
+  5=Version controlled and replayed against historical anomalies before release)
+* Output Range (0-50)</t>
+  </si>
+  <si>
     <t xml:space="preserve">* Define data quality (complete, valid, etc.)
 * Manual quality checks
 * Automated checks (null % on required fields/tags)
@@ -1459,6 +1525,9 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
   </si>
   <si>
@@ -1514,6 +1583,9 @@
   </si>
   <si>
     <t>0: No alerting to any owners</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-14)</t>
   </si>
   <si>
     <t>0: Never</t>
@@ -2867,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2896,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2925,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -2954,7 +3026,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -2983,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3014,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3046,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3078,10 +3150,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3110,10 +3182,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3142,10 +3214,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3176,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3205,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3234,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3263,10 +3335,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3295,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3326,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3355,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3384,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3413,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3442,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3471,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3502,10 +3574,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3534,10 +3606,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3566,10 +3638,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3598,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3630,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3661,10 +3733,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3693,10 +3765,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3725,10 +3797,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3757,10 +3829,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3789,10 +3861,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3821,10 +3893,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3855,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3884,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3913,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -3942,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -3971,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4000,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4031,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4060,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4092,10 +4164,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4124,10 +4196,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4160,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4189,10 +4261,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4221,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4244,13 +4316,16 @@
         <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
+      <c r="G47" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="H47" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4273,13 +4348,16 @@
         <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
+      <c r="G48" s="1" t="s">
+        <v>350</v>
+      </c>
       <c r="H48" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4308,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4337,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4366,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4395,10 +4473,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4427,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4456,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4485,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4516,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4545,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4574,7 +4652,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4603,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4632,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4661,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4692,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4721,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4750,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4779,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4808,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4837,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4868,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4897,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -4926,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -4955,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -4984,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5013,10 +5091,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5047,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5076,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5105,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5134,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5163,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5192,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5225,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5254,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5283,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5312,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5341,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5370,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5401,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5430,7 +5508,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5459,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5488,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5517,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5546,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5577,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5600,16 +5678,16 @@
         <v>274</v>
       </c>
       <c r="E93" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5632,13 +5710,13 @@
         <v>275</v>
       </c>
       <c r="E94" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5667,10 +5745,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5699,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5728,10 +5806,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5762,10 +5840,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5794,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5826,10 +5904,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5858,10 +5936,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5890,10 +5968,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -5922,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -5951,10 +6029,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -5985,10 +6063,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6017,10 +6095,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6049,10 +6127,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6081,10 +6159,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6113,10 +6191,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6145,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6178,10 +6256,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6210,10 +6288,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6242,10 +6320,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6274,10 +6352,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6306,10 +6384,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6338,10 +6416,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6370,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6401,10 +6479,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6433,10 +6511,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6465,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6493,8 +6571,11 @@
       <c r="F121">
         <v>1</v>
       </c>
+      <c r="G121" s="1" t="s">
+        <v>375</v>
+      </c>
       <c r="H121" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6522,8 +6603,11 @@
       <c r="F122">
         <v>1</v>
       </c>
+      <c r="G122" s="1" t="s">
+        <v>376</v>
+      </c>
       <c r="H122" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6552,10 +6636,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6583,8 +6667,11 @@
       <c r="F124">
         <v>1</v>
       </c>
+      <c r="G124" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="H124" s="1" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6615,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6644,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6673,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6702,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6731,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6760,10 +6847,10 @@
         <v>1</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6792,10 +6879,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6824,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6847,13 +6934,13 @@
         <v>314</v>
       </c>
       <c r="E133" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6884,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -6913,10 +7000,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -6945,10 +7032,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -6977,7 +7064,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -7006,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -7035,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -7064,7 +7151,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7243,10 +7330,10 @@
       <formula1>"0: No documented method,10: Documented method of assessing modernization efforts"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
       <formula1>"0: Not done,10: Completed"</formula1>
@@ -7465,16 +7552,16 @@
       <formula1>"0: No alerting to any owners,1: Alerting in at least one owner,3: Alerting to some owners [&gt;20%],6: Alerting to most owners [&gt;60%],10: Alerting to all owners [100%]"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H121">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H122">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: item 1 completed,4: items 1-2 completed,6: items 1-3 completed,8: items 1-4 completed,10: items 1-5 completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H123">
       <formula1>"0: No items completed,2: 1 item completed,3: 2 items completed,4: 3 items completed,5: 4 items completed,7: 5 items completed,8: 6 items completed,9: 7 items completed,10: 8 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H124">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H125">
       <formula1>"0: Not done,10: Completed"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="445">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -151,7 +151,7 @@
     <t>action</t>
   </si>
   <si>
-    <t>Draft Cloud Financial Policies</t>
+    <t>Define Technology Financial Policies</t>
   </si>
   <si>
     <t>Publish Guidelines &amp; Guardrails</t>
@@ -163,7 +163,7 @@
     <t>Monitor Compliance &amp; Report Breaches</t>
   </si>
   <si>
-    <t>Iterate Policies Based on Feedback</t>
+    <t>Iterate Policies on Outcomes &amp; Risk</t>
   </si>
   <si>
     <t>Define Assessment Scope &amp; Goals</t>
@@ -532,6 +532,9 @@
     <t>Define Data Granularity &amp; Frequency</t>
   </si>
   <si>
+    <t>Define Data Ingestion Requirements</t>
+  </si>
+  <si>
     <t>Document Normalization Rules</t>
   </si>
   <si>
@@ -544,9 +547,6 @@
     <t>Optimize Pipelines for Timeliness</t>
   </si>
   <si>
-    <t>Define Data Ingestion Requirements</t>
-  </si>
-  <si>
     <t>Gather Requirements &amp; Define KPIs</t>
   </si>
   <si>
@@ -949,6 +949,9 @@
     <t>004</t>
   </si>
   <si>
+    <t>135</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
@@ -961,9 +964,6 @@
     <t>008</t>
   </si>
   <si>
-    <t>135</t>
-  </si>
-  <si>
     <t>016</t>
   </si>
   <si>
@@ -985,25 +985,80 @@
     <t>022</t>
   </si>
   <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>1.8.0</t>
+  </si>
+  <si>
+    <t>1.1.0</t>
+  </si>
+  <si>
     <t>1.0.0</t>
   </si>
   <si>
-    <t>1.8.0</t>
-  </si>
-  <si>
-    <t>1.1.0</t>
-  </si>
-  <si>
     <t>2.1.0</t>
   </si>
   <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
     <t>1.9.0</t>
   </si>
   <si>
     <t>1.6.1</t>
+  </si>
+  <si>
+    <t>Measured over: every policy in force during the review period. A policy set is small enough to
+enumerate, so items are assessed against each policy rather than as a coverage rate.
+* Policy register (policies in force are listed in one place, each with a named owner and an effective
+  date)
+* Risk named (each policy records the financial risk it exists to reduce)
+* Scope stated (each policy records which FinOps Scopes and technology categories it applies to)
+* Approval recorded (each policy records who approved it and at what level of authority)
+* Next review dated (each policy carries the date by which it is reviewed again)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Guardrail coverage (score x4),
+  Enforcement mode (score x3),
+  Guideline publication (score x2),
+  Exception path (score x1).
+  Max raw (50)
+* Share of routine technology decisions that pass through an automated guardrail
+  (0=Not measured, 1&lt;20%, 2=20-39%, 3=40-59%, 4=60-79%, 5=80% or higher)
+* How a guardrail responds when a decision breaches policy
+  (0=No guardrails, 1=Reported after the fact, 2=Warns the requester, 3=Warns and notifies the owner,
+  4=Blocks the breach with an override path, 5=Blocks and remediates the drift automatically)
+* Where guidelines are published and who can reach them
+  (0=Unpublished, 1=Shared on request, 2=Published to the FinOps team,
+  3=Published to the personas each guideline binds, 4=Reachable from the tools where decisions are
+  made, 5=Versioned, with changes announced to the personas they bind)
+* How an exception is requested and bounded
+  (0=No exception path, 1=Granted informally, 2=Requested and recorded, 3=Approved by a named role,
+  4=Carries an expiry date, 5=Reviewed at expiry and either renewed with rationale or withdrawn)
+* Output Range (0-50)</t>
+  </si>
+  <si>
+    <t>Measured over: every policy in force during the review period, and the personas each one binds.
+* Expectations delivered (each policy has been communicated to the personas it binds, not only to the
+  FinOps team)
+* Exception path communicated (the personas a policy binds know how to request an exception, who
+  decides, and how long one lasts)
+* Risk acceptance recorded (where a policy is waived or a breach is tolerated, the leader accepting
+  that risk is named in the record)
+* Handover covered (a new owner receives the policies that bind their scope when they take ownership)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: every policy in force during the review period, and every change made to one.
+* Review cadence published (the policy set is reviewed on a stated cadence with a named owner)
+* Outcome data feeds the review (adherence rate, breach counts, and guardrail false positives are
+  inputs to it rather than reported separately)
+* Feedback path open (the personas a policy binds can raise an issue through a stated route, and
+  those issues reach the review)
+* Change recorded (each policy change records its rationale and effective date)
+* Retirement path exists (a policy can be withdrawn through a stated route, and each review records
+  which policies were kept, amended, or withdrawn)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Select which teams or groups are in scope for the planned assessments
@@ -1186,12 +1241,71 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
+    <t>* Weighted sum
+  Effective savings rate (score x4),
+  Commitment coverage (score x3),
+  Purchase cadence (score x2),
+  Purchase criteria (score x1).
+  Max raw (50)
+* Effective savings rate achieved on the portfolio, net of unused commitment, scored as a share of
+  the rate the portfolio's own commitment terms make available
+  (expected rate = 25% + 7.5% x (weighted-average commitment term in years - 1), so one-year terms
+  expect 25%, two-year 32.5%, and three-year 40%)
+  (0=Not measured, 1&lt;50%, 2=50-69%, 3=70-84%, 4=85-99%, 5=100% or higher)
+* Share of eligible usage covered by a commitment over the review period
+  (0=Not measured, 1&lt;25%, 2=25-49%, 3=50-69%, 4=70-84%, 5=85% or higher)
+* How often commitments are purchased rather than left to renew in bulk
+  (0=None purchased, 1=One-off, 2=Annual, 3=Quarterly, 4=Monthly or more often,
+  5=Purchases triggered automatically by coverage and utilization reporting)
+* Which numeric tests a purchase must pass before approval
+  (0=None, 1=A savings target stated informally, 2=Savings per dollar of commitment recorded,
+  3=Break-even window also recorded, 4=Expected usage life recorded and the term justified against it,
+  5=All three applied to each decision and the portfolio rebalanced against realized usage)
+* Output Range (0-50)</t>
+  </si>
+  <si>
+    <t>Measured over: every commitment held during the review period, and every commitment expiring in it.
+A portfolio is small enough to enumerate, so items are assessed against each commitment rather than as
+a coverage rate.
+* Return reported (the return on each commitment is reported in currency or as an effective savings
+  rate)
+* Coverage reported (the share of eligible usage covered by commitments is reported for the period)
+* Decline alerting (an alert fires to a named recipient when utilization falls below the level
+  recorded in the commitment strategy)
+* Expiration register (every commitment carries an expiry date and a named owner)
+* Advance notice (owners of expiring commitments are notified at least one full purchase cycle before
+  expiry)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every commitment held during the review period. These are few enough to enumerate, so
+items are assessed against each commitment rather than as a coverage rate.
+* Amortized view published (commitment cost is reported spread across the commitment term rather than
+  landing in the month it is invoiced)
+* Allocation rule documented (how the upfront amount and the remaining term charges reach the teams
+  whose usage the commitment covers, including the treatment of unused commitment)
+* Benefit visible to the team (a team can see the discounted rate it received, not only an aggregate
+  saving for the organization)
+* Unallocated commitment cost reported (the amount no team receives is reported in currency for the
+  period)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>* Process for evaluating spot periodically
 * Tag for date last reviewed
 * New deployments get reviewed beforehand
 * Define requirements for spot
 * Have exception process and expiration date
 10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Purpose recorded (the decisions the forecast exists to support, and the stakeholders who agreed them)
+* Technique recorded (static, trend-based, or driver-based, stated for each organizational level the
+  forecast is produced at)
+* Cadence requirement recorded (when a forecast is due, and how often it is expected to be updated)
+* Horizon recorded (how far forward the forecast reaches, how much history feeds it, and at what
+  granularity)
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Collect data based on existing patterns observed in spend
@@ -1322,6 +1436,16 @@
 * Remove untagged resources after time threshold
 * Block deployments without proper tags
 * Automatically tag based on CI/CD creator and team
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: every change to metadata, hierarchy, or shared cost rules made during the review period.
+Changes are few enough to enumerate, so items are assessed against each one rather than as a coverage
+rate.
+* Recurring review (the allocation strategy is reviewed on a published cadence with a named owner)
+* Change record (every change carries a rationale and an effective date)
+* Advance notice (every change reaches affected resource and budget owners before the effective date)
+* Carried gaps (each review records the gaps it did not close, and the next review lists them)
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1435,24 +1559,30 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not monitored'}, {'Score': 2, 'Condition': 'Reported'}, {'Score': 5, 'Condition': 'Manual remediation'}, {'Score': 10, 'Condition': 'Automated remediation'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': '0 items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': '1 item completed'}, {'Score': 5, 'Condition': '2 items completed'}, {'Score': 8, 'Condition': '3 items completed'}, {'Score': 10, 'Condition': '4 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 4, 'Condition': '1 item completed'}, {'Score': 7, 'Condition': '2 items completed'}, {'Score': 10, 'Condition': '3 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
@@ -1468,9 +1598,6 @@
     <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 6, 'Condition': '3 items completed'}, {'Score': 8, 'Condition': '4 items completed'}, {'Score': 10, 'Condition': '5 items completed'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
   </si>
   <si>
@@ -1525,9 +1652,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 3, 'Condition': '2 items completed'}, {'Score': 4, 'Condition': '3 items completed'}, {'Score': 5, 'Condition': '4 items completed'}, {'Score': 7, 'Condition': '5 items completed'}, {'Score': 8, 'Condition': '6 items completed'}, {'Score': 9, 'Condition': '7 items completed'}, {'Score': 10, 'Condition': '8 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-14)'}, {'Score': 4, 'Condition': 'Developing, Score Range (15-30)'}, {'Score': 7, 'Condition': 'Established, Score Range (31-42)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (43-50)'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Never'}, {'Score': 1, 'Condition': 'Monthly or greater'}, {'Score': 2, 'Condition': 'More than a week'}, {'Score': 3, 'Condition': '7 days'}, {'Score': 4, 'Condition': '5 days'}, {'Score': 6, 'Condition': '2 days'}, {'Score': 8, 'Condition': '1 day'}, {'Score': 10, 'Condition': 'Instant'}]</t>
   </si>
   <si>
@@ -1537,18 +1661,21 @@
     <t>[{'Score': 0, 'Condition': 'No alerting in workflow tools'}, {'Score': 1, 'Condition': 'Alerting in at least one tool'}, {'Score': 3, 'Condition': 'Alerting in some tooling [&gt;20%]'}, {'Score': 6, 'Condition': 'Alerting in most tooling [&gt;60%]'}, {'Score': 10, 'Condition': 'Alerting in all workflow tools [100%]'}]</t>
   </si>
   <si>
+    <t>0: No items completed</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-14)</t>
+  </si>
+  <si>
+    <t>0: Not monitored</t>
+  </si>
+  <si>
+    <t>0: 0 items completed</t>
+  </si>
+  <si>
     <t>0: Not done</t>
   </si>
   <si>
-    <t>0: Not monitored</t>
-  </si>
-  <si>
-    <t>0: 0 items completed</t>
-  </si>
-  <si>
-    <t>0: No items completed</t>
-  </si>
-  <si>
     <t>0: Low Maturity (0-9)</t>
   </si>
   <si>
@@ -1583,9 +1710,6 @@
   </si>
   <si>
     <t>0: No alerting to any owners</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-14)</t>
   </si>
   <si>
     <t>0: Never</t>
@@ -2938,8 +3062,11 @@
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -2967,8 +3094,11 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -2996,8 +3126,11 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -3026,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3054,8 +3187,11 @@
       <c r="F6">
         <v>1</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3086,10 +3222,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3118,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3150,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3182,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3208,16 +3344,16 @@
         <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3242,13 +3378,13 @@
         <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3271,13 +3407,13 @@
         <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3300,13 +3436,13 @@
         <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3335,10 +3471,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3361,13 +3497,13 @@
         <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3398,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3421,13 +3557,13 @@
         <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3450,13 +3586,13 @@
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3479,13 +3615,13 @@
         <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3508,13 +3644,13 @@
         <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3537,13 +3673,13 @@
         <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3568,16 +3704,16 @@
         <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3600,16 +3736,16 @@
         <v>205</v>
       </c>
       <c r="E24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3638,10 +3774,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3670,10 +3806,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3696,13 +3832,13 @@
         <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3733,10 +3869,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3765,10 +3901,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3797,10 +3933,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3829,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3861,10 +3997,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -3893,10 +4029,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -3921,13 +4057,13 @@
         <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -3950,13 +4086,13 @@
         <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -3985,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -4008,13 +4144,13 @@
         <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -4037,13 +4173,13 @@
         <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4072,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4103,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4126,16 +4262,16 @@
         <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4158,16 +4294,16 @@
         <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4190,16 +4326,16 @@
         <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4232,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4261,10 +4397,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4293,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4316,16 +4452,16 @@
         <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4348,16 +4484,16 @@
         <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4380,13 +4516,13 @@
         <v>230</v>
       </c>
       <c r="E49" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4409,13 +4545,13 @@
         <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4438,13 +4574,13 @@
         <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4473,10 +4609,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4499,13 +4635,13 @@
         <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4528,13 +4664,13 @@
         <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4557,13 +4693,13 @@
         <v>236</v>
       </c>
       <c r="E55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4588,13 +4724,13 @@
         <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4617,13 +4753,13 @@
         <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4646,13 +4782,13 @@
         <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4675,13 +4811,13 @@
         <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4704,13 +4840,13 @@
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4733,13 +4869,13 @@
         <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4770,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4793,13 +4929,13 @@
         <v>244</v>
       </c>
       <c r="E63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4822,13 +4958,13 @@
         <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4857,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -4880,13 +5016,13 @@
         <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -4909,13 +5045,13 @@
         <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -4946,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -4975,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -5003,8 +5139,11 @@
       <c r="F70">
         <v>1</v>
       </c>
+      <c r="G70" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="H70" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -5032,8 +5171,11 @@
       <c r="F71">
         <v>1</v>
       </c>
+      <c r="G71" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H71" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5061,8 +5203,11 @@
       <c r="F72">
         <v>1</v>
       </c>
+      <c r="G72" s="1" t="s">
+        <v>358</v>
+      </c>
       <c r="H72" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5091,10 +5236,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5119,13 +5264,13 @@
         <v>255</v>
       </c>
       <c r="E74" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5154,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5183,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5206,13 +5351,13 @@
         <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5235,13 +5380,13 @@
         <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5264,13 +5409,13 @@
         <v>260</v>
       </c>
       <c r="E79" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5297,13 +5442,13 @@
         <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5326,13 +5471,13 @@
         <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5355,13 +5500,13 @@
         <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5384,13 +5529,13 @@
         <v>264</v>
       </c>
       <c r="E83" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5419,7 +5564,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5442,13 +5587,13 @@
         <v>266</v>
       </c>
       <c r="E85" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5479,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5508,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5531,13 +5676,13 @@
         <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5560,13 +5705,13 @@
         <v>270</v>
       </c>
       <c r="E89" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5589,13 +5734,13 @@
         <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5618,13 +5763,13 @@
         <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5654,8 +5799,11 @@
       <c r="F92">
         <v>1</v>
       </c>
+      <c r="G92" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H92" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5684,10 +5832,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5716,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5745,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5777,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5806,10 +5954,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5840,10 +5988,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -5872,10 +6020,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -5904,10 +6052,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -5936,10 +6084,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -5968,10 +6116,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -6000,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -6029,10 +6177,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6063,10 +6211,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6095,10 +6243,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6127,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6159,10 +6307,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6191,10 +6339,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6223,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6256,10 +6404,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6288,10 +6436,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6320,10 +6468,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6352,10 +6500,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6384,10 +6532,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6416,10 +6564,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6447,8 +6595,11 @@
       <c r="F117">
         <v>1</v>
       </c>
+      <c r="G117" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="H117" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6479,10 +6630,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6511,10 +6662,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6543,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6566,16 +6717,16 @@
         <v>302</v>
       </c>
       <c r="E121" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6598,16 +6749,16 @@
         <v>303</v>
       </c>
       <c r="E122" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6636,10 +6787,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6662,16 +6813,16 @@
         <v>305</v>
       </c>
       <c r="E124" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6696,13 +6847,13 @@
         <v>306</v>
       </c>
       <c r="E125" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6725,13 +6876,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6754,13 +6905,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6789,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6812,13 +6963,13 @@
         <v>310</v>
       </c>
       <c r="E129" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6841,16 +6992,13 @@
         <v>311</v>
       </c>
       <c r="E130" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
-      <c r="G130" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="H130" s="1" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -6879,10 +7027,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -6905,13 +7053,16 @@
         <v>313</v>
       </c>
       <c r="E132" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
+      <c r="G132" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="H132" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -6934,13 +7085,13 @@
         <v>314</v>
       </c>
       <c r="E133" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -6965,13 +7116,13 @@
         <v>315</v>
       </c>
       <c r="E134" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7000,10 +7151,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -7032,10 +7183,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -7058,13 +7209,13 @@
         <v>318</v>
       </c>
       <c r="E137" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F137">
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -7093,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -7116,13 +7267,13 @@
         <v>320</v>
       </c>
       <c r="E139" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -7145,13 +7296,13 @@
         <v>321</v>
       </c>
       <c r="E140" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7195,19 +7346,19 @@
   </mergeCells>
   <dataValidations count="139">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
       <formula1>"0: Not monitored,2: Reported,5: Manual remediation,10: Automated remediation"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7">
       <formula1>"0: 0 items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -7399,13 +7550,13 @@
       <formula1>"0: Not done,10: Policy in place and published"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H70">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H71">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H72">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H73">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7465,7 +7616,7 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H92">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H93">
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
@@ -7540,7 +7691,7 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H117">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7576,19 +7727,19 @@
       <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H129">
+      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H130">
-      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H131">
       <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H132">
+      <formula1>"0: No items completed,2: 1 items completed,3: 2 items completed,5: 3 items completed,6: 4 items completed,8: 5 items completed,9: 6 items completed,10: 7 items completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
       <formula1>"0: Not done,10: Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H133">
-      <formula1>"0: Never,1: Monthly or greater,2: More than a week,3: 7 days,4: 5 days,6: 2 days,8: 1 day,10: Instant"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H134">
       <formula1>"0: Not done,10: Completed"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="464">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -1098,6 +1098,67 @@
 10*Ceil(x/2)</t>
   </si>
   <si>
+    <t>* Operating model recorded (which shape the team takes, whether a single central team, a fully virtual
+  team, or a hub and spoke with members embedded in Engineering, and where it reports)
+* Staffing plan recorded (the roles the practice needs, requested against filled, and which support is
+  virtual rather than hired)
+* Skills mapped (leadership, communication, analytical, and technical skills mapped to the roles, with
+  the gaps named)
+* Funding source named (the team has a standing budget line rather than a one-off allocation)
+* Decision model documented (how a cross-functional or urgent decision gets made, and who makes it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the roadmap in force during the review period, and the items on its backlog.
+* Roadmap published (a roadmap for building the practice exists where the personas it affects can
+  read it)
+* Items carry an owner and a date (each backlog item names who is accountable and when it is due)
+* Prioritization stated (the rule used to order the backlog is written down, so two people ordering
+  it reach the same result)
+* Dependencies recorded (items blocked by another capability, a tool, or a hire say so)
+* Progress reviewed (completed and slipped items are reviewed on a stated cadence with a named owner)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the forecasting, budgeting, and procurement workflows the organization runs.
+* Forecasting consumes cost data (the forecast is built from the same cost data the practice
+  publishes, not a separate extract)
+* Budgeting consumes cost data (budget setting and tracking draw on it)
+* Procurement consumes cost data (renewal and purchase decisions see current and committed spend)
+* Delivered where the work happens (the data reaches each workflow in the tool its owners already
+  use rather than a FinOps report they must seek out)
+* Freshness stated (each workflow records how current the data it receives is)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the KPI set the practice publishes during the review period.
+* Published on a cadence (the KPI set is issued on a stated schedule rather than on request)
+* Reaches beyond the practice (the personas each KPI concerns receive it, not only the FinOps team)
+* Value of the practice included (at least one KPI reports the savings or cost avoidance the
+  practice generated)
+* Definitions travel with the numbers (each KPI states what it measures and over what period)
+* Movement explained (a change in a KPI is published with the reason, not only the new figure)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice works with during the review period.
+* Named contacts (each persona the practice depends on has a named counterpart on both sides)
+* Regular contact (engagement happens on a stated cadence rather than when something breaks)
+* Wins published (savings and avoided cost are reported with the team that earned them named)
+* Misses published (targets that were missed are reported in the same place as the wins)
+* Requests tracked (a request to the practice carries an owner and a response, so a persona can see
+  what happened to it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the tasks the practice performs more than once during the review period.
+* Repeated tasks inventoried (the tasks the practice repeats are listed, with how often each runs)
+* Effort recorded (each repeated task carries an estimate of the time it consumes)
+* Automation candidates ranked (tasks are ordered by effort saved against cost to automate)
+* Effect measured (time or cycle time before and after an automation is recorded)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
     <t>* Weighted sum
   Criteria document (score x3),
   KPI alignment (score x3),
@@ -1194,6 +1255,76 @@
 10*Ceil(x/3)</t>
   </si>
   <si>
+    <t>Measured over: every provider invoice received during the review period. Invoices arrive on a monthly
+cycle and are few enough to enumerate, so items are assessed against each one.
+* Intake defined (which provider invoices arrive, on what cycle, and who receives them)
+* Allocation mapping in place (invoice lines resolve to a cost center through the allocation model)
+* Ledger codes mapped (each cost type carries the general ledger code Finance posts it to)
+* Format and timing agreed (the output matches what accounting needs and arrives before close)
+* Unmapped lines reported (invoice lines that resolve to no cost center are reported in currency)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every provider invoice received during the review period.
+* Reconciliation cadence published (invoices are reconciled on a stated cadence with a named owner)
+* Scope stated (reconciliation covers rates, discounts, and credits rather than the total alone)
+* Completion measured against an SLA (the time from invoice receipt to reconciliation complete is
+  measured against a stated target)
+* Discrepancies recorded (each discrepancy carries its amount, its cause, and how it was resolved)
+* Finance reconciles independently (Finance completes a reconciliation without the central FinOps team
+  doing it for them)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Finance approval recorded (Finance is named in the chargeback rules and has signed off on them)
+* Allocation rules documented (which cost types reach which cost centers, including shared costs and
+  commitment discounts)
+* Showback and chargeback scope stated (which scopes are shown for information and which post to
+  official accounting budgets)
+* Cadence documented (when the run happens relative to financial close, and when cost centers receive
+  their figures)
+* Correction path documented (how a posted charge is corrected after close, including true-up entries)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Scored at the highest stage the chargeback run reaches. A practice does not need the stages below it,
+because a run integrated into finance tooling has already replaced the spreadsheet it grew out of.</t>
+  </si>
+  <si>
+    <t>Measured over: every chargeback report issued during the review period, and every dispute raised
+against one.
+* Recipients named (each cost center has a named recipient for its report)
+* Distribution tied to close (reports reach recipients on a stated schedule relative to financial
+  close)
+* Cycle time measured (the time from close to report delivered is measured against a stated target)
+* Accuracy published with the report (recipients see the accuracy figure alongside their charges
+  rather than it being held internally)
+* Dispute outcomes recorded (each dispute records what was challenged, how it resolved, and whether
+  the charge changed)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>* Weighted sum
+  Chargeback accuracy (score x4),
+  Shared cost coverage (score x3),
+  Variance resolution (score x2),
+  Coverage reviewed (score x1).
+  Max raw (50)
+* Variance between what was charged and what was actually consumed, as a share of the amount charged
+  (0=Not measured, 1&gt;20%, 2=10-20%, 3=5-9%, 4=2-4%, 5 under 2%)
+* Share of shared cost allocated to the cost centers consuming it rather than held centrally
+  (0=Not measured, 1=None allocated, 2 under 25%, 3=25-49%, 4=50-79%, 5=80% or higher)
+* What happens to a variance once it is found
+  (0=Absorbed centrally without record, 1=Recorded, 2=Owner named,
+  3=Corrected by a true-up entry in the next close, 4=Root cause recorded against the correction,
+  5=Root cause feeds a change to the allocation rules)
+* How coverage is reviewed
+  (0=Not reviewed, 1=Discussed informally, 2=Reported for the period,
+  3=Reviewed with Finance on a stated cadence, 4=Candidate shared costs are listed with a reason for
+  each exclusion, 5=The exclusion list is worked down against a plan)
+* Output Range (0-50)</t>
+  </si>
+  <si>
     <t>* Document decision rights and approval authority for technology spend
 * Define and publish spend guardrails with named owners
 * Establish escalation path for spend exceptions
@@ -1210,6 +1341,22 @@
 * Deliver cost and outcome comparisons for competing initiatives at reviews
 * Track and report action follow-through from investment decisions
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>Measured over: the review process itself for items 1 to 3, and every review conducted during the
+period for items 4 and 5. Reviews are few enough to enumerate, so those two are assessed against each
+review rather than as a coverage rate.
+* Intake trigger defined (which designs enter review: new builds, material changes, and spend above a
+  stated threshold)
+* Triage signals stated (candidates are prioritized using spend, usage, value, and adoption signals
+  rather than order of arrival)
+* Trade-off model documented (the review weighs cost, value, sovereignty, resilience, and
+  sustainability)
+* Approver named (the role that approves a placement decision and accepts its trade-offs is recorded
+  for each review)
+* Model updated from outcomes (the review records whether what was built matched what was approved,
+  and the trade-off model changes when it did not)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Define process to address notifications from CSPs
@@ -1239,6 +1386,69 @@
 * Train teams on process
 * Automate process
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>x = Resources and SaaS products requiring a license that are mapped to the specific entitlement
+covering them
+y = All resources and SaaS products identified as requiring a license
+x / y</t>
+  </si>
+  <si>
+    <t>Measured over: every license and SaaS agreement held during the review period.
+* Model recorded (each agreement records whether it is an organizational agreement, perpetual,
+  as-a-service, or a marketplace purchase)
+* Change terms recorded (whether licenses can be added mid-contract, and when they can be reduced)
+* Metered charges recorded (charges beyond the license itself, such as access counts, API calls, or
+  stored data)
+* Bring your own license eligibility tagged (resources running software under an existing license
+  carry a tag identifying them)
+* Allocation target named (each agreement records the cost center its cost reaches)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the license and SaaS billing and entitlement feeds in use during the review period.
+* Retrieved without a person (billing arrives on a schedule rather than being downloaded by hand)
+* Normalized schema (billing arrives in a common format such as FOCUS rather than per vendor
+  exports)
+* Entitlements joined (purchased quantities sit alongside the spend, so utilization can be computed)
+* Shared with asset management (contracts, usage and spend are available to the IT and software
+  asset management functions rather than held inside FinOps)
+* Named counterparts (Procurement, Finance and asset management each have a named contact)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every license and SaaS entitlement held during the review period.
+* Compliance checked (resources requiring a license are checked against the entitlements held, and
+  the shortfall or surplus is recorded)
+* Idle assignment identified (assigned licenses with no activity are identified against a stated
+  inactivity window)
+* Reclamation threshold stated (the usage level at which a license is reclaimed or reassigned is
+  written down)
+* Reclamation path exists (a license below the threshold can be reclaimed or reassigned through a
+  stated route, and each review records what was reclaimed, reassigned, or kept)
+* Triggers fire without a person (reclamation starts from the usage data rather than from somebody
+  remembering to look)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: every workload design reviewed during the period that consumes licensed software.
+* License position supplied (the review receives what the organization already owns and what it
+  would need)
+* Options compared (the same workload is costed under infrastructure with an existing license,
+  a managed platform service, and a SaaS product)
+* Compliance checked (the design states whether the license terms permit the deployment)
+* Decision recorded (the option chosen and the licensing reason behind it are written into the
+  design record)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the license and SaaS reporting issued during the review period.
+* Published on a stated cadence (the report is issued on a schedule rather than on request)
+* Spend included (license and SaaS spend for the period, split by agreement)
+* Utilization included (assigned licenses divided by purchased licenses, as a rate)
+* Reaches the holders (the teams holding the licenses receive it, not only Procurement and Finance)
+* Renewal horizon shown (agreements approaching renewal are listed with their dates)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>* Weighted sum
@@ -1586,9 +1796,6 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Defined'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
   </si>
   <si>
@@ -1601,30 +1808,30 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Done and clearly defined'}]</t>
+    <t>[{'Score': 0, 'Condition': 'Assembled in spreadsheets and posted by manual journal entry'}, {'Score': 2, 'Condition': 'Centralized tooling produces the figures, which are then exported and edited by hand'}, {'Score': 5, 'Condition': 'The run is automated end to end and a person posts the result'}, {'Score': 7, 'Condition': 'The run posts to the financial system, with a person reviewing before release'}, {'Score': 10, 'Condition': 'Chargeback and showback reporting is integrated automatically into finance tooling, with exceptions routed for review'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 1, 'Condition': 'Annual'}, {'Score': 2, 'Condition': 'Quarterly'}, {'Score': 5, 'Condition': 'Monthly'}, {'Score': 7, 'Condition': 'Bi-Weekly'}, {'Score': 8, 'Condition': 'Weekly'}, {'Score': 10, 'Condition': 'Daily'}]</t>
   </si>
   <si>
@@ -1685,22 +1892,25 @@
     <t>0: Low Maturity. Score Range (0-15)</t>
   </si>
   <si>
+    <t>0: Assembled in spreadsheets and posted by manual journal entry</t>
+  </si>
+  <si>
     <t>0: No executive sponsor identified</t>
   </si>
   <si>
+    <t>0: No documented method</t>
+  </si>
+  <si>
+    <t>0: 0%</t>
+  </si>
+  <si>
+    <t>0: No teardown/shutdown policy</t>
+  </si>
+  <si>
+    <t>0: No review of trends</t>
+  </si>
+  <si>
     <t>0: Does not exist</t>
-  </si>
-  <si>
-    <t>0: No documented method</t>
-  </si>
-  <si>
-    <t>0: 0%</t>
-  </si>
-  <si>
-    <t>0: No teardown/shutdown policy</t>
-  </si>
-  <si>
-    <t>0: No review of trends</t>
   </si>
   <si>
     <t>0: None</t>
@@ -3066,7 +3276,7 @@
         <v>329</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -3098,7 +3308,7 @@
         <v>330</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -3130,7 +3340,7 @@
         <v>331</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -3159,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3191,7 +3401,7 @@
         <v>332</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3225,7 +3435,7 @@
         <v>333</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3257,7 +3467,7 @@
         <v>334</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3289,7 +3499,7 @@
         <v>335</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3321,7 +3531,7 @@
         <v>336</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3353,7 +3563,7 @@
         <v>337</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3384,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3413,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3442,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3474,7 +3684,7 @@
         <v>338</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3503,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3528,13 +3738,16 @@
         <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="H17" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3557,13 +3770,16 @@
         <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
+      <c r="G18" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="H18" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3586,13 +3802,16 @@
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H19" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3615,13 +3834,16 @@
         <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
+      <c r="G20" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3644,13 +3866,16 @@
         <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
+      <c r="G21" s="1" t="s">
+        <v>343</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3673,13 +3898,16 @@
         <v>203</v>
       </c>
       <c r="E22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
+      <c r="G22" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="H22" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3710,10 +3938,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3742,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -3774,10 +4002,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -3806,10 +4034,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -3838,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -3869,10 +4097,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -3901,10 +4129,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -3933,10 +4161,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -3965,10 +4193,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -3997,10 +4225,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -4029,10 +4257,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -4057,13 +4285,16 @@
         <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="H34" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -4086,13 +4317,16 @@
         <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
+      <c r="G35" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="H35" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -4115,13 +4349,16 @@
         <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H36" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -4144,13 +4381,16 @@
         <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
+      <c r="G37" s="1" t="s">
+        <v>358</v>
+      </c>
       <c r="H37" s="1" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -4173,13 +4413,16 @@
         <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
+      <c r="G38" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="H38" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4202,13 +4445,16 @@
         <v>220</v>
       </c>
       <c r="E39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
+      <c r="G39" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="H39" s="1" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4239,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4268,10 +4514,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4300,10 +4546,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4332,10 +4578,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4362,13 +4608,16 @@
         <v>225</v>
       </c>
       <c r="E44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
+      <c r="G44" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="H44" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4397,10 +4646,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4429,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4458,10 +4707,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4490,10 +4739,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4522,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4551,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4580,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4609,10 +4858,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4641,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4670,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4699,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4730,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -4759,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -4788,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -4817,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -4846,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -4875,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -4900,13 +5149,16 @@
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
+      <c r="G62" s="1" t="s">
+        <v>369</v>
+      </c>
       <c r="H62" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -4929,13 +5181,16 @@
         <v>244</v>
       </c>
       <c r="E63" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
+      <c r="G63" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="H63" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -4958,13 +5213,16 @@
         <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
+      <c r="G64" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="H64" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -4987,13 +5245,16 @@
         <v>246</v>
       </c>
       <c r="E65" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
+      <c r="G65" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="H65" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -5016,13 +5277,16 @@
         <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
+      <c r="G66" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="H66" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -5045,13 +5309,16 @@
         <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
+      <c r="G67" s="1" t="s">
+        <v>374</v>
+      </c>
       <c r="H67" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -5082,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -5111,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -5140,10 +5407,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -5172,10 +5439,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5204,10 +5471,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5236,10 +5503,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5270,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5299,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5328,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5357,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5386,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5415,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5448,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5477,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5506,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5535,7 +5802,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5564,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5593,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5624,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5653,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5682,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5711,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -5740,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -5769,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -5800,10 +6067,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -5832,10 +6099,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -5864,7 +6131,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -5893,10 +6160,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -5925,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -5954,10 +6221,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -5988,10 +6255,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -6020,10 +6287,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -6052,10 +6319,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -6084,10 +6351,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -6116,10 +6383,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -6148,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -6177,10 +6444,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6211,10 +6478,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6243,10 +6510,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6275,10 +6542,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6307,10 +6574,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6339,10 +6606,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6371,7 +6638,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6404,10 +6671,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6436,10 +6703,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6468,10 +6735,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6500,10 +6767,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6532,10 +6799,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6564,10 +6831,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6596,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6630,10 +6897,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6662,10 +6929,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6694,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6723,10 +6990,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -6755,10 +7022,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -6787,10 +7054,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -6819,10 +7086,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -6853,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -6882,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -6911,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -6940,7 +7207,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -6969,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -6998,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -7027,10 +7294,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -7059,10 +7326,10 @@
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -7091,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -7122,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7151,10 +7418,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -7183,10 +7450,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -7215,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -7244,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -7273,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -7302,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7344,7 +7611,7 @@
     <mergeCell ref="B125:B133"/>
     <mergeCell ref="B134:B140"/>
   </mergeCells>
-  <dataValidations count="139">
+  <dataValidations count="138">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
@@ -7391,22 +7658,22 @@
       <formula1>"0: Not done,10: Completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
-      <formula1>"0: Not done,10: Defined"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23">
       <formula1>"0: Low Maturity (0-9),4: Developing (10-18),7: Established (19-26),10: Optimizing (27-31)"</formula1>
@@ -7442,22 +7709,19 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H34">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H35">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36">
-      <formula1>"0: Not done,10: Done and clearly defined"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H38">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H39">
-      <formula1>"0: Not done,10: Defined"</formula1>
+      <formula1>"0: Low Maturity. Score Range (0-14),4: Developing. Score Range (15-30),7: Established. Score Range (31-42),10: Optimizing. Score Range (43-50)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H40">
       <formula1>"0: No executive sponsor identified,10: Executive sponsor formally identified and actively engaged"</formula1>
@@ -7472,7 +7736,7 @@
       <formula1>"0: No items completed,4: 1 item completed,7: 2 items completed,10: 3 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
-      <formula1>"0: Does not exist,10: Exists"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
@@ -7529,19 +7793,19 @@
       <formula1>"0: 0%,1: 10%,2: 20%,3: 30%,4: 40%,5: 50%,6: 60%,7: 70%,8: 80%,9: 90%,10: Near 100%"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H63">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H64">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H65">
-      <formula1>"0: Not done,10: Policy in place and published"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H66">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H67">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H68">
       <formula1>"0: Not done,10: Policy in place and published"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="468">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -1093,9 +1093,58 @@
 * Periodically reevaluate the gap analysis and priority list based on lessons learned and new business goals.</t>
   </si>
   <si>
-    <t>* Define process for reviewing asking for credits from CSPs
-* Define frequency of review, etc.
-10*Ceil(x/2)</t>
+    <t>Measured over: the personas the practice depends on during the review period.
+* Personas listed (the personas the practice depends on are named, not assumed)
+* Need recorded per persona (what each one has to understand to play its part is written down)
+* Current level recorded (what each persona knows today is assessed against that need)
+* Gaps ranked (the gaps are ordered, so the next content produced has a stated reason)
+* Reassessed on a stated cadence (the assessment is repeated on a schedule with a named owner)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice depends on during the review period.
+* Material exists per persona (each persona has content aimed at it rather than one general deck)
+* More than one level (content exists beyond an introduction, so somebody can go further)
+* Organization specific content included (material covers how FinOps works here, not only generic
+  concepts)
+* Onboarding carries it (new employees and contractors receive the material relevant to their
+  persona when they join)
+* Owner named (each curriculum records who maintains it)
+10*Ceil(x/5)</t>
+  </si>
+  <si>
+    <t>Measured over: the learning opportunities offered during the review period.
+* Certification route exists (a funded path to FinOps certification is offered, and who is eligible
+  is written down)
+* Informal sessions run on a stated cadence (office hours, lunch and learns or equivalent, on a
+  schedule rather than when somebody volunteers)
+* Opportunities counted (the number offered in the period is recorded)
+* Open beyond the practice (allied personas can attend, not only the FinOps team)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the vendor and provider training the practice points people to during the review
+period.
+* Catalogued per persona (the vendor training relevant to each persona is listed, with its cost and
+  the effort it takes)
+* Access arranged (people can reach the training without seeking approval each time, and who pays
+  is recorded)
+* Contextualized (each listed course carries a note on what applies here, including which services
+  the organization actually runs and which parts to skip)
+* Catalogue rechecked (the list is reviewed on a stated cadence, because vendors retire and replace
+  courses without telling anyone)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: the personas the practice depends on, and the learning material published to them.
+* Completion measured (the share of each persona that finished the material intended for it)
+* Consultation measured (how often teams return to the material after the session that introduced
+  it)
+* Effect on a named measure reported (training is reported against a KPI it was meant to move, such
+  as tagging compliance or forecast accuracy)
+* Refresh path exists (material is reviewed on a stated cadence, and each review records what was
+  updated, retired, or kept)
+10*Ceil(x/4)</t>
   </si>
   <si>
     <t>* Operating model recorded (which shape the team takes, whether a single central team, a fully virtual
@@ -1790,63 +1839,63 @@
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 3, 'Condition': 'item 1 completed'}, {'Score': 5, 'Condition': 'items 1-2 completed'}, {'Score': 8, 'Condition': 'items 1-3 completed'}, {'Score': 10, 'Condition': 'items 1-4 completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Completed'}]</t>
   </si>
   <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Assembled in spreadsheets and posted by manual journal entry'}, {'Score': 2, 'Condition': 'Centralized tooling produces the figures, which are then exported and edited by hand'}, {'Score': 5, 'Condition': 'The run is automated end to end and a person posts the result'}, {'Score': 7, 'Condition': 'The run posts to the financial system, with a person reviewing before release'}, {'Score': 10, 'Condition': 'Chargeback and showback reporting is integrated automatically into finance tooling, with exceptions routed for review'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 1, 'Condition': 'Annual'}, {'Score': 2, 'Condition': 'Quarterly'}, {'Score': 5, 'Condition': 'Monthly'}, {'Score': 7, 'Condition': 'Bi-Weekly'}, {'Score': 8, 'Condition': 'Weekly'}, {'Score': 10, 'Condition': 'Daily'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No alerting'}, {'Score': 10, 'Condition': 'Alerting exists'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
+  </si>
+  <si>
+    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
+  </si>
+  <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
   </si>
   <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity (0-9)'}, {'Score': 4, 'Condition': 'Developing (10-18)'}, {'Score': 7, 'Condition': 'Established (19-26)'}, {'Score': 10, 'Condition': 'Optimizing (27-31)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-8)'}, {'Score': 4, 'Condition': 'Developing, Score Range (9-17)'}, {'Score': 7, 'Condition': 'Established, Score Range (18-24)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (25-29)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Low Maturity, Score Range (0-15)'}, {'Score': 4, 'Condition': 'Developing, Score Range (16-31)'}, {'Score': 7, 'Condition': 'Established, Score Range (32-44)'}, {'Score': 10, 'Condition': 'Optimizing, Score Range (45-52)'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': 'item 1 completed'}, {'Score': 4, 'Condition': 'items 1-2 completed'}, {'Score': 6, 'Condition': 'items 1-3 completed'}, {'Score': 8, 'Condition': 'items 1-4 completed'}, {'Score': 10, 'Condition': 'items 1-5 completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Assembled in spreadsheets and posted by manual journal entry'}, {'Score': 2, 'Condition': 'Centralized tooling produces the figures, which are then exported and edited by hand'}, {'Score': 5, 'Condition': 'The run is automated end to end and a person posts the result'}, {'Score': 7, 'Condition': 'The run posts to the financial system, with a person reviewing before release'}, {'Score': 10, 'Condition': 'Chargeback and showback reporting is integrated automatically into finance tooling, with exceptions routed for review'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No executive sponsor identified'}, {'Score': 10, 'Condition': 'Executive sponsor formally identified and actively engaged'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No documented method'}, {'Score': 10, 'Condition': 'Documented method of assessing modernization efforts'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80%'}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Not done'}, {'Score': 10, 'Condition': 'Policy in place and published'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No teardown/shutdown policy'}, {'Score': 3, 'Condition': 'Published policy'}, {'Score': 6, 'Condition': 'Classification tagged or otherwise identifiable'}, {'Score': 10, 'Condition': 'Enforced Policy with tagged/identifiable classifications'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No review of trends'}, {'Score': 3, 'Condition': 'Manual review of trends'}, {'Score': 6, 'Condition': 'Automated trend detection'}, {'Score': 10, 'Condition': 'Manual review and automated trend detection'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'Does not exist'}, {'Score': 10, 'Condition': 'Exists'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 1, 'Condition': 'Annual'}, {'Score': 2, 'Condition': 'Quarterly'}, {'Score': 5, 'Condition': 'Monthly'}, {'Score': 7, 'Condition': 'Bi-Weekly'}, {'Score': 8, 'Condition': 'Weekly'}, {'Score': 10, 'Condition': 'Daily'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No alerting'}, {'Score': 10, 'Condition': 'Alerting exists'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': 'item 1 completed'}, {'Score': 10, 'Condition': 'item 2 completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
-  </si>
-  <si>
     <t>[{'Score': 0, 'Condition': '0%'}, {'Score': 1, 'Condition': '10%'}, {'Score': 2, 'Condition': '20%'}, {'Score': 3, 'Condition': '30%'}, {'Score': 4, 'Condition': '40%'}, {'Score': 5, 'Condition': '50%'}, {'Score': 6, 'Condition': '60%'}, {'Score': 7, 'Condition': '70%'}, {'Score': 8, 'Condition': '80% '}, {'Score': 9, 'Condition': '90%'}, {'Score': 10, 'Condition': 'Near 100%'}]</t>
   </si>
   <si>
@@ -1880,16 +1929,16 @@
     <t>0: 0 items completed</t>
   </si>
   <si>
+    <t>0: Low Maturity (0-9)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-8)</t>
+  </si>
+  <si>
+    <t>0: Low Maturity. Score Range (0-15)</t>
+  </si>
+  <si>
     <t>0: Not done</t>
-  </si>
-  <si>
-    <t>0: Low Maturity (0-9)</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-8)</t>
-  </si>
-  <si>
-    <t>0: Low Maturity. Score Range (0-15)</t>
   </si>
   <si>
     <t>0: Assembled in spreadsheets and posted by manual journal entry</t>
@@ -3276,7 +3325,7 @@
         <v>329</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -3308,7 +3357,7 @@
         <v>330</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -3340,7 +3389,7 @@
         <v>331</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -3369,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3401,7 +3450,7 @@
         <v>332</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3435,7 +3484,7 @@
         <v>333</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3467,7 +3516,7 @@
         <v>334</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3499,7 +3548,7 @@
         <v>335</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3531,7 +3580,7 @@
         <v>336</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3563,7 +3612,7 @@
         <v>337</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3588,10 +3637,13 @@
         <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F12">
         <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>448</v>
@@ -3617,10 +3669,13 @@
         <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F13">
         <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>448</v>
@@ -3646,10 +3701,13 @@
         <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F14">
         <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>448</v>
@@ -3675,16 +3733,16 @@
         <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3707,10 +3765,13 @@
         <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F16">
         <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>448</v>
@@ -3744,10 +3805,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3776,10 +3837,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3808,10 +3869,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3840,10 +3901,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3872,10 +3933,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3904,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3938,10 +3999,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -3970,10 +4031,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -4002,10 +4063,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -4034,10 +4095,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -4066,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -4097,10 +4158,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -4129,10 +4190,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -4161,10 +4222,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -4193,10 +4254,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -4225,10 +4286,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -4257,10 +4318,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -4291,10 +4352,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -4323,10 +4384,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -4355,10 +4416,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -4387,10 +4448,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -4419,10 +4480,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4451,10 +4512,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4485,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4514,10 +4575,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4546,10 +4607,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4578,10 +4639,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4614,10 +4675,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4646,10 +4707,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4678,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4707,10 +4768,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4739,10 +4800,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4771,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4800,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4829,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4858,10 +4919,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4890,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4919,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -4948,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -4979,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -5008,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -5037,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -5066,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -5095,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -5124,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -5155,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -5187,10 +5248,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -5219,10 +5280,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -5251,10 +5312,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -5283,10 +5344,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -5315,10 +5376,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -5349,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -5378,7 +5439,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -5407,10 +5468,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -5439,10 +5500,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5471,10 +5532,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5503,10 +5564,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5537,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5566,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5595,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5624,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5653,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5682,7 +5743,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5715,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5744,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5773,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5802,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5831,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5860,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5891,7 +5952,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5920,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -5949,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -5978,7 +6039,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -6007,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -6036,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -6067,10 +6128,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -6099,10 +6160,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -6131,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -6160,10 +6221,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -6192,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -6221,10 +6282,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -6255,10 +6316,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -6287,10 +6348,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -6319,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -6351,10 +6412,10 @@
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -6383,10 +6444,10 @@
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -6415,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -6444,10 +6505,10 @@
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6478,10 +6539,10 @@
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6510,10 +6571,10 @@
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6542,10 +6603,10 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6574,10 +6635,10 @@
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6606,10 +6667,10 @@
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6638,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6671,10 +6732,10 @@
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6703,10 +6764,10 @@
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6735,10 +6796,10 @@
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6767,10 +6828,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6799,10 +6860,10 @@
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6831,10 +6892,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6863,10 +6924,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6897,10 +6958,10 @@
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6929,10 +6990,10 @@
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -6961,7 +7022,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -6990,10 +7051,10 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -7022,10 +7083,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -7054,10 +7115,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -7086,10 +7147,10 @@
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -7120,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -7149,7 +7210,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -7178,7 +7239,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -7207,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -7236,7 +7297,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -7265,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -7294,10 +7355,10 @@
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -7326,10 +7387,10 @@
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -7358,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -7389,7 +7450,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7418,10 +7479,10 @@
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -7450,10 +7511,10 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -7482,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -7511,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -7540,7 +7601,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -7569,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7643,19 +7704,19 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15">
-      <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H16">
-      <formula1>"0: Not done,10: Completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H17">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>

--- a/assessments/FinOps Foundation/assessment.xlsx
+++ b/assessments/FinOps Foundation/assessment.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="471">
   <si>
     <t>Sum of Weights</t>
   </si>
@@ -988,16 +988,16 @@
     <t>2.0.0</t>
   </si>
   <si>
+    <t>1.1.0</t>
+  </si>
+  <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
+    <t>2.1.0</t>
+  </si>
+  <si>
     <t>1.8.0</t>
-  </si>
-  <si>
-    <t>1.1.0</t>
-  </si>
-  <si>
-    <t>1.0.0</t>
-  </si>
-  <si>
-    <t>2.1.0</t>
   </si>
   <si>
     <t>1.9.0</t>
@@ -1047,6 +1047,11 @@
   that risk is named in the record)
 * Handover covered (a new owner receives the policies that bind their scope when they take ownership)
 10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Scored at the highest stage the practice reaches for policy breaches. The stages replace one
+another: a practice remediating automatically is not also waiting to be told.
+Measured over: the policies in force during the review period and the resources they bind.</t>
   </si>
   <si>
     <t>Measured over: every policy in force during the review period, and every change made to one.
@@ -1612,10 +1617,20 @@
 2. Compare carbon calculations with targets for new projects and overall consumption</t>
   </si>
   <si>
-    <t>* Define and follow process for gathering deployment plans from teams
-* Determine timeline for each new project to adjust the forecast during that time
-* Determine how optimizations and lower run rate will impact the forecast on a rolling basis
+    <t>Measured over: the projects and optimization work feeding the forecast during the review period. These
+are few enough to enumerate, so items are assessed against each one rather than as a coverage rate.
+* Define and follow process for gathering deployment plans from teams (the process names who submits
+  plans, on what cadence, and in what form)
+* Determine timeline for each new project to adjust the forecast during that time (each project carries
+  start and ramp dates, so its spend lands in the periods it occurs in)
+* Determine how optimizations and lower run rate will impact the forecast on a rolling basis (committed
+  optimization work is carried into the forecast as a reduction on a stated schedule)
 10*Ceil(x/3)</t>
+  </si>
+  <si>
+    <t>x = Estimates whose actual cost landed inside the variance threshold set for them
+y = All estimates made whose actual cost is now known
+x / y</t>
   </si>
   <si>
     <t>* Refer teams to Documented Estimating Scope &amp; Policy and include these methods in trainings
@@ -1625,10 +1640,15 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
-    <t>* Define cost drivers from finance/business
-* Gather metrics on a cadence
-* Set goals/targets
-* Set up forecasting and anomaly detection on units
+    <t>Measured over: the unit metrics the practice has defined. A practice holds few enough units to
+enumerate, so items are assessed against each unit metric rather than as a coverage rate.
+* Define cost drivers from finance/business (the business volume that drives cost is named with Finance,
+  such as orders, users or transactions)
+* Gather metrics on a cadence (the volume is collected on a stated schedule with a named owner rather
+  than pulled on request)
+* Set goals/targets (each unit metric carries a target value and the period that target applies to)
+* Set up forecasting and anomaly detection on units (the unit metric itself is forecast and alerted on,
+  not only the absolute spend behind it)
 10*Ceil(x/4)</t>
   </si>
   <si>
@@ -1664,6 +1684,16 @@
 * Unit economics influence the decisions in build vs buy, architecture design, workload placement,
   migration, sourcing, pricing, etc.
 10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t>Measured over: every unit cost improvement communicated during the review period.
+* Evidence recorded (each win records the baseline, what was changed, and the outcome)
+* Unit named (the win states which unit metric moved, not only a currency amount)
+* Measurement type separated (avoidance, savings and cost reduction are reported as distinct
+  figures rather than one total)
+* Team credited (the team whose change produced the result is named)
+* Delivered per persona (each audience receives it in the channel it already uses)
+10*Ceil(x/5)</t>
   </si>
   <si>
     <t>Increasing Granularity and Visibility
@@ -1708,22 +1738,38 @@
 10*Ceil(x/4)</t>
   </si>
   <si>
-    <t>* Manual inspection of spikes
-* Out-of-the-box tool based anomaly alerts
-* Custom simple increase alert calculations
-* Custom alerts per business unit, team, etc.
-* Alerts per unit costs above thresholds
-10*Ceil(x/5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Defined severity tiers
-* Thresholds associated with severity tiers are defined
-* Defined and adhered to response SLAs
-* Published response runbooks
-* Runbook percent successful or completed
-* RCA completed after alerts
+    <t>* Out-of-the-box tool based anomaly alerts (the anomaly detection shipped by the provider or cost tool
+  is enabled)
+* Custom simple increase alert calculations (the practice defines its own increase threshold, stating the
+  comparison period and the percentage or amount that triggers it)
+* Custom alerts per business unit, team, etc. (alert scopes are set per business unit, team or
+  application rather than only on the total)
+* Alerts per unit costs above thresholds (an alert is configured against a unit cost metric with a stated
+  threshold)
+10*Ceil(x/4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured over: the severity tiers the practice defines, and every runbook execution during the review
+period for item 5. A tier set is small enough to enumerate, so items 1 to 4 are assessed against each
+tier rather than as a coverage rate.
+* Defined severity tiers (a fixed set of named severity levels exists)
+* Thresholds associated with severity tiers are defined (each tier carries a number that places an
+  anomaly in it, such as a variance amount or a percentage)
+* Defined and adhered to response SLAs (each tier carries a response time target, and adherence against
+  it is reported for the period)
+* Published response runbooks (a runbook exists per tier or anomaly type and is reachable by whoever
+  responds)
+* Runbook percent successful or completed (the share of runbook executions that resolved the case
+  without improvisation is measured)
+* RCA completed after alerts (a root cause analysis is recorded for the severity tiers that call for one)
 10*Ceil(x/6)
 </t>
+  </si>
+  <si>
+    <t>x = Resource and budget owners who receive anomaly alerts for the scopes they own, routed
+automatically
+y = All owners whose scopes anomaly detection covers
+x / y</t>
   </si>
   <si>
     <t>Denominator: all anomalies detected during the review period. A field item is met when the field is
@@ -1752,14 +1798,22 @@
 10*Ceil(x/5)</t>
   </si>
   <si>
-    <t>* Number of detections per time period
-* Number of detections over threshold
-* Time to send notifications to stakeholders
-* Time to validate anomaly
-* Resolution Time/SLA adherence
-* False positive rate
-* Cost Avoidance due to detection
-* Percent anomalies addressed
+    <t>Measured over: the measures themselves. An item is met when the measure is reported for the review
+period.
+* Number of detections per time period (the count of anomalies detected is reported per period)
+* Number of detections over threshold (the count exceeding a stated materiality threshold is reported
+  separately from the total)
+* Time to send notifications to stakeholders (elapsed time from detection to the notification reaching a
+  named recipient)
+* Time to validate anomaly (elapsed time from notification to a recorded disposition of true, expected
+  or false)
+* Resolution Time/SLA adherence (elapsed time to resolution, reported against the response SLA set in
+  action 24)
+* False positive rate (anomalies dispositioned false as a share of all anomalies detected)
+* Cost Avoidance due to detection (the variance amount avoided, from the variance rate and how long the
+  anomaly ran before it was fixed)
+* Percent anomalies addressed (anomalies carrying a recorded remediation as a share of those
+  dispositioned true)
 10*Ceil(x/8)</t>
   </si>
   <si>
@@ -1888,9 +1942,6 @@
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 2, 'Condition': '1 item completed'}, {'Score': 4, 'Condition': '2 items completed'}, {'Score': 5, 'Condition': '3 items completed'}, {'Score': 7, 'Condition': '4 items completed'}, {'Score': 9, 'Condition': '5 items completed'}, {'Score': 10, 'Condition': '6 items completed'}]</t>
-  </si>
-  <si>
-    <t>[{'Score': 0, 'Condition': 'None'}, {'Score': 10, 'Condition': 'communicates wins in KPI thresholds and unit costs'}]</t>
   </si>
   <si>
     <t>[{'Score': 0, 'Condition': 'No items completed'}, {'Score': 5, 'Condition': '1 item completed'}, {'Score': 10, 'Condition': '2 items completed'}]</t>
@@ -3325,7 +3376,7 @@
         <v>329</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I2">
         <f>F2*VALUE(LEFT(H2, FIND(":", H2)-1))</f>
@@ -3357,7 +3408,7 @@
         <v>330</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I3">
         <f>F3*VALUE(LEFT(H3, FIND(":", H3)-1))</f>
@@ -3389,7 +3440,7 @@
         <v>331</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I4">
         <f>F4*VALUE(LEFT(H4, FIND(":", H4)-1))</f>
@@ -3412,13 +3463,16 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="I5">
         <f>F5*VALUE(LEFT(H5, FIND(":", H5)-1))</f>
@@ -3447,10 +3501,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I6">
         <f>F6*VALUE(LEFT(H6, FIND(":", H6)-1))</f>
@@ -3475,16 +3529,16 @@
         <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I7">
         <f>F7*VALUE(LEFT(H7, FIND(":", H7)-1))</f>
@@ -3507,16 +3561,16 @@
         <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I8">
         <f>F8*VALUE(LEFT(H8, FIND(":", H8)-1))</f>
@@ -3539,16 +3593,16 @@
         <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I9">
         <f>F9*VALUE(LEFT(H9, FIND(":", H9)-1))</f>
@@ -3571,16 +3625,16 @@
         <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I10">
         <f>F10*VALUE(LEFT(H10, FIND(":", H10)-1))</f>
@@ -3603,16 +3657,16 @@
         <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I11">
         <f>F11*VALUE(LEFT(H11, FIND(":", H11)-1))</f>
@@ -3643,10 +3697,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I12">
         <f>F12*VALUE(LEFT(H12, FIND(":", H12)-1))</f>
@@ -3675,10 +3729,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I13">
         <f>F13*VALUE(LEFT(H13, FIND(":", H13)-1))</f>
@@ -3707,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I14">
         <f>F14*VALUE(LEFT(H14, FIND(":", H14)-1))</f>
@@ -3739,10 +3793,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I15">
         <f>F15*VALUE(LEFT(H15, FIND(":", H15)-1))</f>
@@ -3771,10 +3825,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I16">
         <f>F16*VALUE(LEFT(H16, FIND(":", H16)-1))</f>
@@ -3805,10 +3859,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I17">
         <f>F17*VALUE(LEFT(H17, FIND(":", H17)-1))</f>
@@ -3837,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I18">
         <f>F18*VALUE(LEFT(H18, FIND(":", H18)-1))</f>
@@ -3869,10 +3923,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I19">
         <f>F19*VALUE(LEFT(H19, FIND(":", H19)-1))</f>
@@ -3901,10 +3955,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I20">
         <f>F20*VALUE(LEFT(H20, FIND(":", H20)-1))</f>
@@ -3933,10 +3987,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I21">
         <f>F21*VALUE(LEFT(H21, FIND(":", H21)-1))</f>
@@ -3965,10 +4019,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I22">
         <f>F22*VALUE(LEFT(H22, FIND(":", H22)-1))</f>
@@ -3993,16 +4047,16 @@
         <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I23">
         <f>F23*VALUE(LEFT(H23, FIND(":", H23)-1))</f>
@@ -4025,16 +4079,16 @@
         <v>205</v>
       </c>
       <c r="E24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="I24">
         <f>F24*VALUE(LEFT(H24, FIND(":", H24)-1))</f>
@@ -4057,16 +4111,16 @@
         <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I25">
         <f>F25*VALUE(LEFT(H25, FIND(":", H25)-1))</f>
@@ -4089,16 +4143,16 @@
         <v>207</v>
       </c>
       <c r="E26" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I26">
         <f>F26*VALUE(LEFT(H26, FIND(":", H26)-1))</f>
@@ -4121,13 +4175,13 @@
         <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I27">
         <f>F27*VALUE(LEFT(H27, FIND(":", H27)-1))</f>
@@ -4152,16 +4206,16 @@
         <v>209</v>
       </c>
       <c r="E28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I28">
         <f>F28*VALUE(LEFT(H28, FIND(":", H28)-1))</f>
@@ -4184,16 +4238,16 @@
         <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I29">
         <f>F29*VALUE(LEFT(H29, FIND(":", H29)-1))</f>
@@ -4216,16 +4270,16 @@
         <v>211</v>
       </c>
       <c r="E30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I30">
         <f>F30*VALUE(LEFT(H30, FIND(":", H30)-1))</f>
@@ -4248,16 +4302,16 @@
         <v>212</v>
       </c>
       <c r="E31" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I31">
         <f>F31*VALUE(LEFT(H31, FIND(":", H31)-1))</f>
@@ -4280,16 +4334,16 @@
         <v>213</v>
       </c>
       <c r="E32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I32">
         <f>F32*VALUE(LEFT(H32, FIND(":", H32)-1))</f>
@@ -4312,16 +4366,16 @@
         <v>214</v>
       </c>
       <c r="E33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I33">
         <f>F33*VALUE(LEFT(H33, FIND(":", H33)-1))</f>
@@ -4352,10 +4406,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I34">
         <f>F34*VALUE(LEFT(H34, FIND(":", H34)-1))</f>
@@ -4384,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I35">
         <f>F35*VALUE(LEFT(H35, FIND(":", H35)-1))</f>
@@ -4416,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I36">
         <f>F36*VALUE(LEFT(H36, FIND(":", H36)-1))</f>
@@ -4448,10 +4502,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I37">
         <f>F37*VALUE(LEFT(H37, FIND(":", H37)-1))</f>
@@ -4480,10 +4534,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I38">
         <f>F38*VALUE(LEFT(H38, FIND(":", H38)-1))</f>
@@ -4512,10 +4566,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I39">
         <f>F39*VALUE(LEFT(H39, FIND(":", H39)-1))</f>
@@ -4540,13 +4594,13 @@
         <v>221</v>
       </c>
       <c r="E40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="I40">
         <f>F40*VALUE(LEFT(H40, FIND(":", H40)-1))</f>
@@ -4569,16 +4623,16 @@
         <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I41">
         <f>F41*VALUE(LEFT(H41, FIND(":", H41)-1))</f>
@@ -4601,16 +4655,16 @@
         <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I42">
         <f>F42*VALUE(LEFT(H42, FIND(":", H42)-1))</f>
@@ -4633,16 +4687,16 @@
         <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I43">
         <f>F43*VALUE(LEFT(H43, FIND(":", H43)-1))</f>
@@ -4675,10 +4729,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I44">
         <f>F44*VALUE(LEFT(H44, FIND(":", H44)-1))</f>
@@ -4701,16 +4755,16 @@
         <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I45">
         <f>F45*VALUE(LEFT(H45, FIND(":", H45)-1))</f>
@@ -4733,13 +4787,13 @@
         <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I46">
         <f>F46*VALUE(LEFT(H46, FIND(":", H46)-1))</f>
@@ -4768,10 +4822,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I47">
         <f>F47*VALUE(LEFT(H47, FIND(":", H47)-1))</f>
@@ -4800,10 +4854,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I48">
         <f>F48*VALUE(LEFT(H48, FIND(":", H48)-1))</f>
@@ -4826,13 +4880,13 @@
         <v>230</v>
       </c>
       <c r="E49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I49">
         <f>F49*VALUE(LEFT(H49, FIND(":", H49)-1))</f>
@@ -4855,13 +4909,13 @@
         <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I50">
         <f>F50*VALUE(LEFT(H50, FIND(":", H50)-1))</f>
@@ -4884,13 +4938,13 @@
         <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I51">
         <f>F51*VALUE(LEFT(H51, FIND(":", H51)-1))</f>
@@ -4913,16 +4967,16 @@
         <v>233</v>
       </c>
       <c r="E52" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I52">
         <f>F52*VALUE(LEFT(H52, FIND(":", H52)-1))</f>
@@ -4945,13 +4999,13 @@
         <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I53">
         <f>F53*VALUE(LEFT(H53, FIND(":", H53)-1))</f>
@@ -4974,13 +5028,13 @@
         <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I54">
         <f>F54*VALUE(LEFT(H54, FIND(":", H54)-1))</f>
@@ -5003,13 +5057,13 @@
         <v>236</v>
       </c>
       <c r="E55" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I55">
         <f>F55*VALUE(LEFT(H55, FIND(":", H55)-1))</f>
@@ -5034,13 +5088,13 @@
         <v>237</v>
       </c>
       <c r="E56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I56">
         <f>F56*VALUE(LEFT(H56, FIND(":", H56)-1))</f>
@@ -5063,13 +5117,13 @@
         <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I57">
         <f>F57*VALUE(LEFT(H57, FIND(":", H57)-1))</f>
@@ -5092,13 +5146,13 @@
         <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I58">
         <f>F58*VALUE(LEFT(H58, FIND(":", H58)-1))</f>
@@ -5121,13 +5175,13 @@
         <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I59">
         <f>F59*VALUE(LEFT(H59, FIND(":", H59)-1))</f>
@@ -5150,13 +5204,13 @@
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I60">
         <f>F60*VALUE(LEFT(H60, FIND(":", H60)-1))</f>
@@ -5179,13 +5233,13 @@
         <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I61">
         <f>F61*VALUE(LEFT(H61, FIND(":", H61)-1))</f>
@@ -5216,10 +5270,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I62">
         <f>F62*VALUE(LEFT(H62, FIND(":", H62)-1))</f>
@@ -5248,10 +5302,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I63">
         <f>F63*VALUE(LEFT(H63, FIND(":", H63)-1))</f>
@@ -5280,10 +5334,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I64">
         <f>F64*VALUE(LEFT(H64, FIND(":", H64)-1))</f>
@@ -5312,10 +5366,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I65">
         <f>F65*VALUE(LEFT(H65, FIND(":", H65)-1))</f>
@@ -5344,10 +5398,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I66">
         <f>F66*VALUE(LEFT(H66, FIND(":", H66)-1))</f>
@@ -5376,10 +5430,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I67">
         <f>F67*VALUE(LEFT(H67, FIND(":", H67)-1))</f>
@@ -5404,13 +5458,13 @@
         <v>249</v>
       </c>
       <c r="E68" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I68">
         <f>F68*VALUE(LEFT(H68, FIND(":", H68)-1))</f>
@@ -5433,13 +5487,13 @@
         <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I69">
         <f>F69*VALUE(LEFT(H69, FIND(":", H69)-1))</f>
@@ -5468,10 +5522,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I70">
         <f>F70*VALUE(LEFT(H70, FIND(":", H70)-1))</f>
@@ -5500,10 +5554,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I71">
         <f>F71*VALUE(LEFT(H71, FIND(":", H71)-1))</f>
@@ -5532,10 +5586,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I72">
         <f>F72*VALUE(LEFT(H72, FIND(":", H72)-1))</f>
@@ -5558,16 +5612,16 @@
         <v>254</v>
       </c>
       <c r="E73" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I73">
         <f>F73*VALUE(LEFT(H73, FIND(":", H73)-1))</f>
@@ -5592,13 +5646,13 @@
         <v>255</v>
       </c>
       <c r="E74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I74">
         <f>F74*VALUE(LEFT(H74, FIND(":", H74)-1))</f>
@@ -5621,13 +5675,13 @@
         <v>256</v>
       </c>
       <c r="E75" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="I75">
         <f>F75*VALUE(LEFT(H75, FIND(":", H75)-1))</f>
@@ -5650,13 +5704,13 @@
         <v>257</v>
       </c>
       <c r="E76" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I76">
         <f>F76*VALUE(LEFT(H76, FIND(":", H76)-1))</f>
@@ -5679,13 +5733,13 @@
         <v>258</v>
       </c>
       <c r="E77" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I77">
         <f>F77*VALUE(LEFT(H77, FIND(":", H77)-1))</f>
@@ -5708,13 +5762,13 @@
         <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I78">
         <f>F78*VALUE(LEFT(H78, FIND(":", H78)-1))</f>
@@ -5737,13 +5791,13 @@
         <v>260</v>
       </c>
       <c r="E79" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I79">
         <f>F79*VALUE(LEFT(H79, FIND(":", H79)-1))</f>
@@ -5770,13 +5824,13 @@
         <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I80">
         <f>F80*VALUE(LEFT(H80, FIND(":", H80)-1))</f>
@@ -5799,13 +5853,13 @@
         <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I81">
         <f>F81*VALUE(LEFT(H81, FIND(":", H81)-1))</f>
@@ -5828,13 +5882,13 @@
         <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I82">
         <f>F82*VALUE(LEFT(H82, FIND(":", H82)-1))</f>
@@ -5857,13 +5911,13 @@
         <v>264</v>
       </c>
       <c r="E83" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I83">
         <f>F83*VALUE(LEFT(H83, FIND(":", H83)-1))</f>
@@ -5886,13 +5940,13 @@
         <v>265</v>
       </c>
       <c r="E84" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="I84">
         <f>F84*VALUE(LEFT(H84, FIND(":", H84)-1))</f>
@@ -5915,13 +5969,13 @@
         <v>266</v>
       </c>
       <c r="E85" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I85">
         <f>F85*VALUE(LEFT(H85, FIND(":", H85)-1))</f>
@@ -5946,13 +6000,13 @@
         <v>267</v>
       </c>
       <c r="E86" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I86">
         <f>F86*VALUE(LEFT(H86, FIND(":", H86)-1))</f>
@@ -5975,13 +6029,13 @@
         <v>268</v>
       </c>
       <c r="E87" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I87">
         <f>F87*VALUE(LEFT(H87, FIND(":", H87)-1))</f>
@@ -6004,13 +6058,13 @@
         <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I88">
         <f>F88*VALUE(LEFT(H88, FIND(":", H88)-1))</f>
@@ -6033,13 +6087,13 @@
         <v>270</v>
       </c>
       <c r="E89" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I89">
         <f>F89*VALUE(LEFT(H89, FIND(":", H89)-1))</f>
@@ -6062,13 +6116,13 @@
         <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I90">
         <f>F90*VALUE(LEFT(H90, FIND(":", H90)-1))</f>
@@ -6091,13 +6145,13 @@
         <v>272</v>
       </c>
       <c r="E91" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I91">
         <f>F91*VALUE(LEFT(H91, FIND(":", H91)-1))</f>
@@ -6128,10 +6182,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I92">
         <f>F92*VALUE(LEFT(H92, FIND(":", H92)-1))</f>
@@ -6160,10 +6214,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I93">
         <f>F93*VALUE(LEFT(H93, FIND(":", H93)-1))</f>
@@ -6192,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I94">
         <f>F94*VALUE(LEFT(H94, FIND(":", H94)-1))</f>
@@ -6215,16 +6269,16 @@
         <v>276</v>
       </c>
       <c r="E95" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I95">
         <f>F95*VALUE(LEFT(H95, FIND(":", H95)-1))</f>
@@ -6247,13 +6301,13 @@
         <v>277</v>
       </c>
       <c r="E96" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I96">
         <f>F96*VALUE(LEFT(H96, FIND(":", H96)-1))</f>
@@ -6276,16 +6330,16 @@
         <v>278</v>
       </c>
       <c r="E97" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I97">
         <f>F97*VALUE(LEFT(H97, FIND(":", H97)-1))</f>
@@ -6310,16 +6364,16 @@
         <v>279</v>
       </c>
       <c r="E98" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I98">
         <f>F98*VALUE(LEFT(H98, FIND(":", H98)-1))</f>
@@ -6342,16 +6396,16 @@
         <v>280</v>
       </c>
       <c r="E99" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I99">
         <f>F99*VALUE(LEFT(H99, FIND(":", H99)-1))</f>
@@ -6374,16 +6428,16 @@
         <v>281</v>
       </c>
       <c r="E100" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I100">
         <f>F100*VALUE(LEFT(H100, FIND(":", H100)-1))</f>
@@ -6406,16 +6460,16 @@
         <v>282</v>
       </c>
       <c r="E101" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I101">
         <f>F101*VALUE(LEFT(H101, FIND(":", H101)-1))</f>
@@ -6438,16 +6492,16 @@
         <v>283</v>
       </c>
       <c r="E102" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I102">
         <f>F102*VALUE(LEFT(H102, FIND(":", H102)-1))</f>
@@ -6470,13 +6524,16 @@
         <v>284</v>
       </c>
       <c r="E103" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
+      <c r="G103" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="H103" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I103">
         <f>F103*VALUE(LEFT(H103, FIND(":", H103)-1))</f>
@@ -6499,16 +6556,16 @@
         <v>285</v>
       </c>
       <c r="E104" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I104">
         <f>F104*VALUE(LEFT(H104, FIND(":", H104)-1))</f>
@@ -6533,16 +6590,16 @@
         <v>286</v>
       </c>
       <c r="E105" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I105">
         <f>F105*VALUE(LEFT(H105, FIND(":", H105)-1))</f>
@@ -6565,16 +6622,16 @@
         <v>287</v>
       </c>
       <c r="E106" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I106">
         <f>F106*VALUE(LEFT(H106, FIND(":", H106)-1))</f>
@@ -6597,16 +6654,16 @@
         <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I107">
         <f>F107*VALUE(LEFT(H107, FIND(":", H107)-1))</f>
@@ -6629,16 +6686,16 @@
         <v>289</v>
       </c>
       <c r="E108" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I108">
         <f>F108*VALUE(LEFT(H108, FIND(":", H108)-1))</f>
@@ -6661,16 +6718,16 @@
         <v>290</v>
       </c>
       <c r="E109" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I109">
         <f>F109*VALUE(LEFT(H109, FIND(":", H109)-1))</f>
@@ -6693,13 +6750,16 @@
         <v>291</v>
       </c>
       <c r="E110" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
+      <c r="G110" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="H110" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="I110">
         <f>F110*VALUE(LEFT(H110, FIND(":", H110)-1))</f>
@@ -6726,16 +6786,16 @@
         <v>292</v>
       </c>
       <c r="E111" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I111">
         <f>F111*VALUE(LEFT(H111, FIND(":", H111)-1))</f>
@@ -6758,16 +6818,16 @@
         <v>293</v>
       </c>
       <c r="E112" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I112">
         <f>F112*VALUE(LEFT(H112, FIND(":", H112)-1))</f>
@@ -6790,16 +6850,16 @@
         <v>294</v>
       </c>
       <c r="E113" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I113">
         <f>F113*VALUE(LEFT(H113, FIND(":", H113)-1))</f>
@@ -6822,16 +6882,16 @@
         <v>295</v>
       </c>
       <c r="E114" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I114">
         <f>F114*VALUE(LEFT(H114, FIND(":", H114)-1))</f>
@@ -6854,16 +6914,16 @@
         <v>296</v>
       </c>
       <c r="E115" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I115">
         <f>F115*VALUE(LEFT(H115, FIND(":", H115)-1))</f>
@@ -6886,16 +6946,16 @@
         <v>297</v>
       </c>
       <c r="E116" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I116">
         <f>F116*VALUE(LEFT(H116, FIND(":", H116)-1))</f>
@@ -6924,10 +6984,10 @@
         <v>1</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I117">
         <f>F117*VALUE(LEFT(H117, FIND(":", H117)-1))</f>
@@ -6952,16 +7012,16 @@
         <v>299</v>
       </c>
       <c r="E118" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I118">
         <f>F118*VALUE(LEFT(H118, FIND(":", H118)-1))</f>
@@ -6984,16 +7044,16 @@
         <v>300</v>
       </c>
       <c r="E119" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I119">
         <f>F119*VALUE(LEFT(H119, FIND(":", H119)-1))</f>
@@ -7016,13 +7076,16 @@
         <v>301</v>
       </c>
       <c r="E120" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
+      <c r="G120" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="H120" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I120">
         <f>F120*VALUE(LEFT(H120, FIND(":", H120)-1))</f>
@@ -7045,16 +7108,16 @@
         <v>302</v>
       </c>
       <c r="E121" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I121">
         <f>F121*VALUE(LEFT(H121, FIND(":", H121)-1))</f>
@@ -7077,16 +7140,16 @@
         <v>303</v>
       </c>
       <c r="E122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I122">
         <f>F122*VALUE(LEFT(H122, FIND(":", H122)-1))</f>
@@ -7109,16 +7172,16 @@
         <v>304</v>
       </c>
       <c r="E123" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F123">
         <v>1</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I123">
         <f>F123*VALUE(LEFT(H123, FIND(":", H123)-1))</f>
@@ -7141,16 +7204,16 @@
         <v>305</v>
       </c>
       <c r="E124" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I124">
         <f>F124*VALUE(LEFT(H124, FIND(":", H124)-1))</f>
@@ -7175,13 +7238,13 @@
         <v>306</v>
       </c>
       <c r="E125" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I125">
         <f>F125*VALUE(LEFT(H125, FIND(":", H125)-1))</f>
@@ -7204,13 +7267,13 @@
         <v>307</v>
       </c>
       <c r="E126" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I126">
         <f>F126*VALUE(LEFT(H126, FIND(":", H126)-1))</f>
@@ -7233,13 +7296,13 @@
         <v>308</v>
       </c>
       <c r="E127" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I127">
         <f>F127*VALUE(LEFT(H127, FIND(":", H127)-1))</f>
@@ -7262,13 +7325,13 @@
         <v>309</v>
       </c>
       <c r="E128" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I128">
         <f>F128*VALUE(LEFT(H128, FIND(":", H128)-1))</f>
@@ -7297,7 +7360,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I129">
         <f>F129*VALUE(LEFT(H129, FIND(":", H129)-1))</f>
@@ -7320,13 +7383,13 @@
         <v>311</v>
       </c>
       <c r="E130" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I130">
         <f>F130*VALUE(LEFT(H130, FIND(":", H130)-1))</f>
@@ -7349,16 +7412,16 @@
         <v>312</v>
       </c>
       <c r="E131" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I131">
         <f>F131*VALUE(LEFT(H131, FIND(":", H131)-1))</f>
@@ -7381,16 +7444,16 @@
         <v>313</v>
       </c>
       <c r="E132" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I132">
         <f>F132*VALUE(LEFT(H132, FIND(":", H132)-1))</f>
@@ -7413,13 +7476,13 @@
         <v>314</v>
       </c>
       <c r="E133" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I133">
         <f>F133*VALUE(LEFT(H133, FIND(":", H133)-1))</f>
@@ -7444,13 +7507,13 @@
         <v>315</v>
       </c>
       <c r="E134" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I134">
         <f>F134*VALUE(LEFT(H134, FIND(":", H134)-1))</f>
@@ -7473,16 +7536,16 @@
         <v>316</v>
       </c>
       <c r="E135" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F135">
         <v>1</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I135">
         <f>F135*VALUE(LEFT(H135, FIND(":", H135)-1))</f>
@@ -7505,16 +7568,16 @@
         <v>317</v>
       </c>
       <c r="E136" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F136">
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I136">
         <f>F136*VALUE(LEFT(H136, FIND(":", H136)-1))</f>
@@ -7537,13 +7600,13 @@
         <v>318</v>
       </c>
       <c r="E137" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F137">
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I137">
         <f>F137*VALUE(LEFT(H137, FIND(":", H137)-1))</f>
@@ -7566,13 +7629,13 @@
         <v>319</v>
       </c>
       <c r="E138" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F138">
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="I138">
         <f>F138*VALUE(LEFT(H138, FIND(":", H138)-1))</f>
@@ -7595,13 +7658,13 @@
         <v>320</v>
       </c>
       <c r="E139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I139">
         <f>F139*VALUE(LEFT(H139, FIND(":", H139)-1))</f>
@@ -7624,13 +7687,13 @@
         <v>321</v>
       </c>
       <c r="E140" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I140">
         <f>F140*VALUE(LEFT(H140, FIND(":", H140)-1))</f>
@@ -7995,7 +8058,7 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H110">
-      <formula1>"0: None,10: communicates wins in KPI thresholds and unit costs"</formula1>
+      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H111">
       <formula1>"0: No items completed,5: 1 item completed,10: 2 items completed"</formula1>
@@ -8019,7 +8082,7 @@
       <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H118">
-      <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,6: 3 items completed,8: 4 items completed,10: 5 items completed"</formula1>
+      <formula1>"0: No items completed,3: 1 item completed,5: 2 items completed,8: 3 items completed,10: 4 items completed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H119">
       <formula1>"0: No items completed,2: 1 item completed,4: 2 items completed,5: 3 items completed,7: 4 items completed,9: 5 items completed,10: 6 items completed"</formula1>
